--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5527,6 +5527,265 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122645337</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rotarbo, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>571825</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6565825</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska hackmärken och observation av spillkråka</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122645442</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5465</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>101377</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stekelbock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Necydalis major</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Rotarbo, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>571871</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6565785</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Kläckhål 5 mm</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122645337</v>
+        <v>122645442</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>5465</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>101377</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5567,11 +5567,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5581,10 +5582,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571825</v>
+        <v>571871</v>
       </c>
       <c r="R39" t="n">
-        <v>6565825</v>
+        <v>6565785</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5616,7 +5617,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5626,12 +5627,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska hackmärken och observation av spillkråka</t>
+          <t>Kläckhål 5 mm</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5658,10 +5659,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122645442</v>
+        <v>122645337</v>
       </c>
       <c r="B40" t="n">
-        <v>5465</v>
+        <v>57399</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5670,25 +5671,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101377</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5696,12 +5697,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571871</v>
+        <v>571825</v>
       </c>
       <c r="R40" t="n">
-        <v>6565785</v>
+        <v>6565825</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Kläckhål 5 mm</t>
+          <t>Färska hackmärken och observation av spillkråka</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5662,7 +5662,7 @@
         <v>122645337</v>
       </c>
       <c r="B40" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122645442</v>
+        <v>122645337</v>
       </c>
       <c r="B39" t="n">
-        <v>5465</v>
+        <v>57400</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101377</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5567,12 +5567,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5582,10 +5581,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571871</v>
+        <v>571825</v>
       </c>
       <c r="R39" t="n">
-        <v>6565785</v>
+        <v>6565825</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5617,7 +5616,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5627,12 +5626,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Kläckhål 5 mm</t>
+          <t>Färska hackmärken och observation av spillkråka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5659,10 +5658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122645337</v>
+        <v>122645442</v>
       </c>
       <c r="B40" t="n">
-        <v>57400</v>
+        <v>5465</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5671,25 +5670,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>101377</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5697,11 +5696,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571825</v>
+        <v>571871</v>
       </c>
       <c r="R40" t="n">
-        <v>6565825</v>
+        <v>6565785</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska hackmärken och observation av spillkråka</t>
+          <t>Kläckhål 5 mm</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122645337</v>
+        <v>122645442</v>
       </c>
       <c r="B39" t="n">
-        <v>57400</v>
+        <v>5465</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>101377</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5567,11 +5567,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5581,10 +5582,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571825</v>
+        <v>571871</v>
       </c>
       <c r="R39" t="n">
-        <v>6565825</v>
+        <v>6565785</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5616,7 +5617,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5626,12 +5627,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska hackmärken och observation av spillkråka</t>
+          <t>Kläckhål 5 mm</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5658,10 +5659,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122645442</v>
+        <v>122645337</v>
       </c>
       <c r="B40" t="n">
-        <v>5465</v>
+        <v>57400</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5670,25 +5671,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101377</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5696,12 +5697,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571871</v>
+        <v>571825</v>
       </c>
       <c r="R40" t="n">
-        <v>6565785</v>
+        <v>6565825</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Kläckhål 5 mm</t>
+          <t>Färska hackmärken och observation av spillkråka</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122645442</v>
+        <v>122645337</v>
       </c>
       <c r="B39" t="n">
-        <v>5465</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101377</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5567,12 +5567,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5582,10 +5581,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571871</v>
+        <v>571825</v>
       </c>
       <c r="R39" t="n">
-        <v>6565785</v>
+        <v>6565825</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5617,7 +5616,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5627,12 +5626,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Kläckhål 5 mm</t>
+          <t>Färska hackmärken och observation av spillkråka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5659,10 +5658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122645337</v>
+        <v>122645442</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
+        <v>5465</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5671,25 +5670,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>101377</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5697,11 +5696,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571825</v>
+        <v>571871</v>
       </c>
       <c r="R40" t="n">
-        <v>6565825</v>
+        <v>6565785</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska hackmärken och observation av spillkråka</t>
+          <t>Kläckhål 5 mm</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5529,10 +5529,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122645337</v>
+        <v>122645442</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>5465</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5541,25 +5541,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>101377</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5567,11 +5567,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5581,10 +5582,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571825</v>
+        <v>571871</v>
       </c>
       <c r="R39" t="n">
-        <v>6565825</v>
+        <v>6565785</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5616,7 +5617,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5626,12 +5627,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska hackmärken och observation av spillkråka</t>
+          <t>Kläckhål 5 mm</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5658,10 +5659,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122645442</v>
+        <v>122645337</v>
       </c>
       <c r="B40" t="n">
-        <v>5465</v>
+        <v>57494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5670,25 +5671,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101377</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5696,12 +5697,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571871</v>
+        <v>571825</v>
       </c>
       <c r="R40" t="n">
-        <v>6565785</v>
+        <v>6565825</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Kläckhål 5 mm</t>
+          <t>Färska hackmärken och observation av spillkråka</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5786,6 +5786,135 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123415135</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57487</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Rotarbo, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>571880</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6565754</v>
+      </c>
+      <c r="S41" t="n">
+        <v>16</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Par mindre hackspett häckar i skogsområdet. Blandskog och nedanför hällmarken ett kärr med lövträd och död ved.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5791,7 +5791,7 @@
         <v>123415135</v>
       </c>
       <c r="B41" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5791,7 +5791,7 @@
         <v>123415135</v>
       </c>
       <c r="B41" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 5064-2020 artfynd.xlsx
+++ b/artfynd/A 5064-2020 artfynd.xlsx
@@ -5791,7 +5791,7 @@
         <v>123415135</v>
       </c>
       <c r="B41" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
